--- a/BeatnotePostHotCell/May22,2026/Fit_ResultMay22.xlsx
+++ b/BeatnotePostHotCell/May22,2026/Fit_ResultMay22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\May22,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB2E8A8-CDBB-493B-BAED-9837D674090A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB0CD4D-C329-45FE-B2E9-F3E7260B2EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>May22,2026+12-08-18PM</t>
-  </si>
-  <si>
-    <t>May22,2026+12-16-38PM</t>
   </si>
   <si>
     <t>May22,2026+12-25-23PM</t>
@@ -492,25 +489,25 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.17068222085432</v>
+        <v>0.13284709830915301</v>
       </c>
       <c r="C2" s="1">
-        <v>1.5030449917016999</v>
+        <v>1.5008292078956</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.7758197433313501</v>
+        <v>-1.1736707772049299E-3</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.55419278114649E-4</v>
+        <v>-1.55419164861235E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>1.6502141266917401</v>
+        <v>1.58902594056027</v>
       </c>
       <c r="G2" s="1">
-        <v>62.4016183734336</v>
+        <v>62.308847898232003</v>
       </c>
       <c r="H2" s="1">
-        <v>1.1473704951315701E-3</v>
+        <v>8.1271146947680902E-4</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75">
@@ -518,25 +515,25 @@
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>0.169252380360598</v>
+        <v>0.13179599174591999</v>
       </c>
       <c r="C3" s="1">
-        <v>1.51920323042476</v>
+        <v>1.5001855323275399</v>
       </c>
       <c r="D3" s="1">
-        <v>-25.0734145598237</v>
+        <v>-1.5169811919692601E-3</v>
       </c>
       <c r="E3" s="2">
-        <v>-3.0250272979636102E-5</v>
+        <v>-3.02461838578949E-5</v>
       </c>
       <c r="F3" s="1">
-        <v>2.1443849296003199</v>
+        <v>2.0832082955257198</v>
       </c>
       <c r="G3" s="1">
-        <v>60.479803459742598</v>
+        <v>60.478910744047397</v>
       </c>
       <c r="H3" s="1">
-        <v>6.5497298644773098E-4</v>
+        <v>5.7857934614656103E-4</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42.75">
@@ -544,25 +541,25 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>0.17600556016018701</v>
+        <v>0.13701539714226199</v>
       </c>
       <c r="C4" s="1">
-        <v>1.52920993816136</v>
+        <v>1.4998587048285199</v>
       </c>
       <c r="D4" s="1">
-        <v>-39.192557678874103</v>
+        <v>-1.49779126312265E-3</v>
       </c>
       <c r="E4" s="2">
-        <v>-1.91081452011005E-5</v>
+        <v>-1.9109213896229199E-5</v>
       </c>
       <c r="F4" s="1">
-        <v>2.14051343679176</v>
+        <v>2.07934444947914</v>
       </c>
       <c r="G4" s="1">
-        <v>62.467392909793702</v>
+        <v>62.463689825000998</v>
       </c>
       <c r="H4" s="1">
-        <v>1.15715385985478E-3</v>
+        <v>8.8438439446781897E-4</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42.75">
@@ -570,25 +567,25 @@
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>0.173810152659294</v>
+        <v>0.13611960900852699</v>
       </c>
       <c r="C5" s="1">
-        <v>1.50421430651999</v>
+        <v>1.49910587386262</v>
       </c>
       <c r="D5" s="1">
-        <v>-7.2581456903972601</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-8.4798885407197602E-5</v>
+        <v>-1.0344100102275401E-3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-1.04861101550095E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>1.8814544214776701</v>
+        <v>2.0881704337788398</v>
       </c>
       <c r="G5" s="1">
-        <v>62.487567853674101</v>
+        <v>62.5113332443632</v>
       </c>
       <c r="H5" s="1">
-        <v>1.1472763620120599E-3</v>
+        <v>1.1571538655554001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42.75">
@@ -596,52 +593,36 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>0.17477778117201601</v>
+        <v>0.13627945937632699</v>
       </c>
       <c r="C6" s="1">
-        <v>1.5016568853985</v>
+        <v>1.50019244453714</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.9322989980155203</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-1.04860922409325E-4</v>
+        <v>-1.24662269658737E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-8.5112567350472396E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>2.14931856126341</v>
+        <v>1.8393553453849201</v>
       </c>
       <c r="G6" s="1">
-        <v>62.511333279972497</v>
+        <v>62.566891827637399</v>
       </c>
       <c r="H6" s="1">
-        <v>1.15715386863295E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42.75">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.17496986858800301</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.5047571334112</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-7.3233066007347203</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-8.5113186280295506E-5</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1.90050482390746</v>
-      </c>
-      <c r="G7" s="1">
-        <v>62.565547165604301</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.07220126946622E-3</v>
-      </c>
+        <v>1.1331890903845899E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -753,7 +734,7 @@
     </row>
     <row r="5" spans="1:8" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
         <v>8.2690216688035498</v>
@@ -777,7 +758,7 @@
     </row>
     <row r="6" spans="1:8" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>8.2739805096279504</v>
@@ -832,16 +813,14 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.17068222085432</v>
+        <v>8.1314875900026795</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1">
-        <v>8.1314875900026795</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+        <v>0.13284709830915301</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
@@ -850,16 +829,14 @@
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>0.169252380360598</v>
+        <v>8.2055994032900799</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1">
-        <v>8.2055994032900799</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
+        <v>0.13179599174591999</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
@@ -868,52 +845,46 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>0.17600556016018701</v>
+        <v>8.2176590050244904</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>8.2176590050244904</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
+        <v>0.13701539714226199</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>0.17477778117201601</v>
+        <v>8.2690216688035498</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1">
-        <v>8.2690216688035498</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1"/>
+        <v>0.13611960900852699</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>0.17496986858800301</v>
+        <v>8.2739805096279504</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
-        <v>8.2739805096279504</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+        <v>0.13627945937632699</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
